--- a/src/attributions/attributions_ig_traj_239.xlsx
+++ b/src/attributions/attributions_ig_traj_239.xlsx
@@ -1571,19 +1571,19 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2170461487869008</v>
+        <v>0.3090452411823946</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05975528358099093</v>
+        <v>0.06858197226475905</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2201138667216569</v>
+        <v>-0.2580937766420587</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1592,55 +1592,55 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04624854970930557</v>
+        <v>0.09468232161605115</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.003803729843468771</v>
+        <v>-0.004537381423014021</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0054426775770867</v>
+        <v>0.005321822482219983</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0121931202114987</v>
+        <v>-0.1056316874383861</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0868252484346145</v>
+        <v>-0.08876752135260182</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.03073929221168106</v>
+        <v>-0.1179686885115422</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
@@ -1649,22 +1649,22 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0382599538654256</v>
+        <v>0.1204909075576635</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1248757428227917</v>
+        <v>0.05574707491768357</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.05272487440239207</v>
+        <v>0.1426421313689668</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1673,40 +1673,40 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04727546788309357</v>
+        <v>0.1240628564336683</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.04069551459811029</v>
+        <v>-0.05468214925075224</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.1266174540529857</v>
+        <v>-0.2334080160793761</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2648216490784184</v>
+        <v>0.6605533326792286</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,25 +1715,25 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.158183454195903</v>
+        <v>-0.2446433548197511</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.4032229626462012</v>
+        <v>-0.4145454973390755</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1258434913437113</v>
+        <v>0.1155903603534005</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0321798712052718</v>
+        <v>0.06354345695446442</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.07420996449020013</v>
+        <v>-0.1682280474042692</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1760,73 +1760,73 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001813804961735719</v>
+        <v>0.07024336343322565</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.02494621923470392</v>
+        <v>0.08542670307367577</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02298061902257294</v>
+        <v>0.1569639767492343</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.07039851144054037</v>
+        <v>0.2210686711751446</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1132601381946213</v>
+        <v>-0.1019873709470566</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.1328434026368685</v>
+        <v>-0.2767261156106648</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1073822586619718</v>
+        <v>-0.2579791212192447</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.03080327952085105</v>
+        <v>-0.06246542476836745</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1152601678946842</v>
+        <v>0.1771601283681623</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1835,58 +1835,58 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.004952620690293392</v>
+        <v>-0.2419717810089807</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.04683927353884149</v>
+        <v>0.05823623442732907</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01088647837865527</v>
+        <v>0.1487782641373321</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.08796629451604106</v>
+        <v>-0.2459956557600103</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01803138483404039</v>
+        <v>-0.05932614306533676</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.1334773349378525</v>
+        <v>0.1517059269718812</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
@@ -1895,73 +1895,73 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.05390966898013396</v>
+        <v>-0.1304530710247239</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03964686353397251</v>
+        <v>-0.05258112797751905</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.004301978598605613</v>
+        <v>0.1386717639002207</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01465169216944954</v>
+        <v>-0.09144986067297706</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1168675655337137</v>
+        <v>0.001259247068048539</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01375070556506886</v>
+        <v>0.07686626210868473</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.05133033603566994</v>
+        <v>0.1531542436854383</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.01138238411469794</v>
+        <v>-0.04031904439138505</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.01486296360789663</v>
+        <v>0.1717622430373899</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1973,25 +1973,25 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.1183834044830427</v>
+        <v>-0.1246728294020258</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.00657862766244103</v>
+        <v>-0.0876946304949535</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.124754724094843</v>
+        <v>0.15251226559154</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
@@ -2000,10 +2000,10 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.04773220213343761</v>
+        <v>-0.1638853005417523</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
@@ -2012,37 +2012,37 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03458485190971846</v>
+        <v>-0.1924983131969843</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.05692480113302847</v>
+        <v>0.1655584447708482</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.08614608822317865</v>
+        <v>-0.2373045676457447</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03335915137871331</v>
+        <v>-0.1187707585295715</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1202570701488062</v>
+        <v>0.1607772201807394</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2054,85 +2054,85 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.07584601399976601</v>
+        <v>-0.1282552618633541</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.06607827494170669</v>
+        <v>-0.06166041973372087</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1369253727303383</v>
+        <v>0.2840597021542615</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.1581160502589445</v>
+        <v>-0.01354226086905758</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.05833573986616377</v>
+        <v>0.06358466761025044</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.08684198627359421</v>
+        <v>0.04977563576019872</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.04502832762619102</v>
+        <v>-0.1201723210806603</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.02892805697973632</v>
+        <v>0.1844128726722734</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06188241556675032</v>
+        <v>0.356990222936502</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,25 +2718,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00919528496563511</v>
+        <v>0.0220525717311173</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02096794634652264</v>
+        <v>-0.139113602231268</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01583180676886485</v>
+        <v>0.1384412850576173</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,40 +2745,40 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.003870392348116805</v>
+        <v>-0.02962947320802266</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01137817643241358</v>
+        <v>-0.08891539115063261</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00221558817205783</v>
+        <v>0.1285754117412413</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.004864649138517006</v>
+        <v>-0.1260306164882175</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001368053858590308</v>
+        <v>-0.03274342816722655</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2790,79 +2790,79 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0109584462755314</v>
+        <v>0.0282460201890781</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0228047992025442</v>
+        <v>-0.2331253679905819</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0007665886333811035</v>
+        <v>0.03407016642560937</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.004387812711740875</v>
+        <v>0.1902961099298199</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01112489320974974</v>
+        <v>0.1350259023472225</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01606030600129673</v>
+        <v>-0.1387497303333746</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.08283945622608539</v>
+        <v>0.7401460792974859</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.004261689772855511</v>
+        <v>-0.212844233455272</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005681785358982464</v>
+        <v>-0.182845444988128</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02782589872503623</v>
+        <v>-0.02603101642158416</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,40 +2880,40 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.019549124877929</v>
+        <v>-0.06256612241091052</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.04848099779482846</v>
+        <v>-0.1058755028573734</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02899641128218291</v>
+        <v>0.04287204020722209</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02612550003476191</v>
+        <v>0.130246068827055</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.004639947585217081</v>
+        <v>0.1469991435735549</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02863953808049267</v>
+        <v>0.371863239996362</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,43 +2934,43 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.005118974974840005</v>
+        <v>-0.03343428744894922</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004552350786474342</v>
+        <v>-0.2357657079612692</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01841412203212578</v>
+        <v>-0.2366367439352777</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002118904109182733</v>
+        <v>-0.02475558903598251</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01906843224728092</v>
+        <v>0.1593026504163285</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.00527981981179559</v>
+        <v>-0.1583482802732657</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.004108655922119841</v>
+        <v>0.08265434223804126</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0007809106633622541</v>
+        <v>-0.0005368565063359071</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01412110748908113</v>
+        <v>-0.2141646274406068</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.003638293946648316</v>
+        <v>-0.02103884702721226</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01873158737210883</v>
+        <v>0.1592680513527125</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,52 +3033,52 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004318032461428666</v>
+        <v>-0.03500064536337061</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01812079702664662</v>
+        <v>-0.07243342027773597</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.003546490182692985</v>
+        <v>0.0381981839502944</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.005923831458935125</v>
+        <v>-0.1004499681973499</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-8.95803137745175e-05</v>
+        <v>0.005045798389804882</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.006199084901461501</v>
+        <v>0.01096105966138417</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,46 +3087,46 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01775048927623112</v>
+        <v>0.08336716842357894</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03205357836121387</v>
+        <v>-0.07633904146178534</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0005930411331872502</v>
+        <v>0.1252512036742044</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01384135386648185</v>
+        <v>-0.04290063506293436</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001024316817494005</v>
+        <v>-0.1298588274190507</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01136739744581012</v>
+        <v>0.08025539296084284</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0151176610700421</v>
+        <v>-0.120314527228706</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,37 +3150,37 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.008658470596225855</v>
+        <v>-0.1981833145509987</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.004997676992950147</v>
+        <v>0.04087401940103448</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01643971944646957</v>
+        <v>-0.2354908320712711</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.004044660982815073</v>
+        <v>-0.06249427331599514</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02020196961973531</v>
+        <v>0.1370694691002747</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3189,13 +3189,13 @@
         <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0001931502163546776</v>
+        <v>-0.2129666420269714</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,70 +3204,70 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02621339499649919</v>
+        <v>0.07817244621478675</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01979613233959642</v>
+        <v>0.224937528140058</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.001545785384382836</v>
+        <v>-0.02923275999523168</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0004305234250826192</v>
+        <v>-0.0009684823460585909</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.008614041637559848</v>
+        <v>0.0984252938980041</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02722373650709928</v>
+        <v>-0.08883527549646714</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.006754551429212806</v>
+        <v>0.1032511967407685</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1219184922435678</v>
+        <v>0.3596587934806102</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00341922424569569</v>
+        <v>0.04701253394394463</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07554215579938897</v>
+        <v>-0.1737893151797207</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04787212156262561</v>
+        <v>0.1972385839958785</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,64 +3314,64 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.001065919297129571</v>
+        <v>-0.02050356167385696</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.04436512974791736</v>
+        <v>-0.1048566585218731</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005346369061070973</v>
+        <v>0.1008062043297155</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01565563709737232</v>
+        <v>-0.1309635511870953</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001837912597843148</v>
+        <v>-0.01664052696451674</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0198400566526704</v>
+        <v>0.04464816045266069</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02141697196959443</v>
+        <v>-0.2257415515704195</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003131864756851275</v>
+        <v>-0.08593729336544681</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02090540267192832</v>
+        <v>0.1649419863892808</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.005648328108760059</v>
+        <v>0.1102783684175098</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.03744228037387603</v>
+        <v>-0.1054153519546961</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1430254650529754</v>
+        <v>0.6314944983237311</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001972021399295735</v>
+        <v>-0.1430461270688154</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0804899250187244</v>
+        <v>-0.1939985228435721</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.05045559657957903</v>
+        <v>-0.00166960569581843</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03946647271976187</v>
+        <v>-0.05358596249987858</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.07253849888305285</v>
+        <v>-0.1598287888623418</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
@@ -3461,28 +3461,28 @@
         <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03371498684132956</v>
+        <v>0.03597891687574522</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01956870652075751</v>
+        <v>0.07254997340886034</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.003965689451432413</v>
+        <v>0.04722070850917186</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.05116806930114831</v>
+        <v>0.308161113444726</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.001303406701031689</v>
+        <v>-0.02883878609189162</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.02388984077286906</v>
+        <v>-0.1354880624237273</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.03740482327755392</v>
+        <v>-0.217174321146221</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.006396417242737202</v>
+        <v>-0.04840076487036296</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.03789734780422618</v>
+        <v>0.1321887507124207</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.006160283191042309</v>
+        <v>-0.1295911565612802</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0132598649037093</v>
+        <v>0.05421167611691716</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002855032719408294</v>
+        <v>0.009374606953762575</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.03239953157570981</v>
+        <v>-0.1940197640021956</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0004151191401548538</v>
+        <v>-0.04769959422431577</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.04071832288578545</v>
+        <v>0.1356734250807938</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3602,19 +3602,19 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.009980225018701914</v>
+        <v>-0.05911762011671604</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.007550856845062566</v>
+        <v>-0.05057888358632381</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001557597627415997</v>
+        <v>0.03674997328495205</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3626,28 +3626,28 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.00469659320587397</v>
+        <v>-0.1073022857837814</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.003814337520042726</v>
+        <v>-0.001245428164752054</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.01283373467887755</v>
+        <v>0.08686405340242774</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,19 +3656,19 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.02192092560421685</v>
+        <v>0.02309928583987801</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.03172828514516485</v>
+        <v>0.1047281624243083</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.003640348428581356</v>
+        <v>0.1229969291436613</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,28 +3677,28 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0329163327992961</v>
+        <v>-0.05047978054719228</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.002021538045435149</v>
+        <v>-0.1002014461203396</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02793303738141083</v>
+        <v>0.04271529679866341</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,64 +3707,64 @@
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0322274775026795</v>
+        <v>-0.1020339593147921</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.007628490835113849</v>
+        <v>-0.1000891848899627</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02848116422246836</v>
+        <v>0.08794312527388219</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.03338839772884131</v>
+        <v>-0.2149313210351812</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.001829895696801994</v>
+        <v>-0.07378981977737391</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03673689978036491</v>
+        <v>0.1200942846639016</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.008528316195541794</v>
+        <v>-0.2422941632775134</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,70 +3773,70 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02280911646014498</v>
+        <v>0.06524182636341437</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0214696168193547</v>
+        <v>0.2489491057001093</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.007765853870291177</v>
+        <v>-0.03214507368865865</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001764752710660483</v>
+        <v>-0.008439801244018977</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02597642590847323</v>
+        <v>0.1364030772445146</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02232209276413775</v>
+        <v>-0.05369989581638961</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.006911032116960865</v>
+        <v>0.009347113875979477</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -4416,154 +4416,154 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2197667908849288</v>
+        <v>0.5578233739821539</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06763846107580557</v>
+        <v>-0.002276327687486007</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04778675991960982</v>
+        <v>0.06526552827665759</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06871271768981697</v>
+        <v>-0.2160888884973607</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1277587378901571</v>
+        <v>0.4993542099199259</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05462433734185475</v>
+        <v>-0.1120233051405439</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02946027265860778</v>
+        <v>-0.04205129660193223</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.04317462987899704</v>
+        <v>-0.1126920379458048</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04937144377824131</v>
+        <v>0.1385991341198753</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01514882904960532</v>
+        <v>-0.1466654076126097</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02754256094888084</v>
+        <v>-0.1434895456064261</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02309280354320864</v>
+        <v>0.006694252528539393</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01840914406672245</v>
+        <v>0.1465613418905699</v>
       </c>
       <c r="AD8" t="n">
         <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04367134585154401</v>
+        <v>-0.3394198412530866</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.00125026988709313</v>
+        <v>-0.2172587604576743</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.0119005617031316</v>
+        <v>-0.1541780242071397</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001656097944060184</v>
+        <v>0.2670730249954267</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.03113131002247291</v>
+        <v>-0.1450366566588353</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01359647667537389</v>
+        <v>0.1670010875248334</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.02883069633471027</v>
+        <v>-0.1910001426642614</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3244104642102168</v>
+        <v>0.8155728531843117</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.009397941958847021</v>
+        <v>-0.004228945384757997</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.04677756664568994</v>
+        <v>-0.1414491872986918</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.04363053488610782</v>
+        <v>-0.1224664155625487</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4572,58 +4572,58 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02025646108011033</v>
+        <v>0.01816792888228675</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.04292178833260405</v>
+        <v>-0.0916837570388969</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.09432179855542493</v>
+        <v>-0.1375731519483069</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.1236468880906035</v>
+        <v>-0.2544931411963827</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.07009425816355222</v>
+        <v>0.03899142412124584</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04521396862708939</v>
+        <v>-0.002509924346538094</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.06597463524192362</v>
+        <v>0.1470223782879805</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01369774018282329</v>
+        <v>0.009761877696496859</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
@@ -4632,19 +4632,19 @@
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1198428804506877</v>
+        <v>0.3776346301940939</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.02495097964529424</v>
+        <v>-0.086450497649896</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01273602252141491</v>
+        <v>-0.009874549155010388</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.02348861010011724</v>
+        <v>-0.1655355969374503</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4653,28 +4653,28 @@
         <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.05866956524858317</v>
+        <v>-0.2702416595451853</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.006510601720493901</v>
+        <v>0.04023978871117893</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.001319947976155638</v>
+        <v>-0.06583626314199072</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04405373934626156</v>
+        <v>0.1165501145961387</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4683,301 +4683,301 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.02195677800762075</v>
+        <v>-0.1933365221164951</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.03441075806007817</v>
+        <v>0.139470317511012</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.01931733497489368</v>
+        <v>0.01906795409302841</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.0164019664527915</v>
+        <v>0.08857434423209844</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.05104901735226843</v>
+        <v>-0.2450263319433091</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02359816977854992</v>
+        <v>0.04563486735221417</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.004730084119904106</v>
+        <v>-0.08257239161756685</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.05180191264958028</v>
+        <v>0.1122135875887873</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.01321611014989833</v>
+        <v>-0.048787806640476</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.07826675187084432</v>
+        <v>-0.02973966325784675</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.01561664936553353</v>
+        <v>0.4731048605914669</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.003009584250383389</v>
+        <v>0.02178720578549196</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.03798320532819007</v>
+        <v>-0.09494536045495842</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.02724777894867367</v>
+        <v>0.06337540368320493</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0227020118237608</v>
+        <v>-0.09776319057018079</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.02653254520503731</v>
+        <v>0.1543843604885614</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.006054731141806383</v>
+        <v>0.1476123856479851</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.002795734057268609</v>
+        <v>0.07060383409165563</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03584555947100912</v>
+        <v>0.01682263222457325</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.00258541826303072</v>
+        <v>-0.01521958738026408</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08593620734471746</v>
+        <v>-0.114526649424992</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.03471547948101402</v>
+        <v>0.07162425893107426</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0367353333852423</v>
+        <v>-0.1009926891466333</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.008353643140979465</v>
+        <v>-0.02670890678746801</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03584935300058535</v>
+        <v>-0.09565654023149291</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0003255704418690113</v>
+        <v>-0.08395119485912086</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.004785980301531378</v>
+        <v>-0.07426719753134392</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.06831097152479307</v>
+        <v>0.2493991858716779</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.04709916610512214</v>
+        <v>-0.2822239029585729</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00705408079461627</v>
+        <v>0.0427143634043378</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01414332293081877</v>
+        <v>-0.1164456146798406</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04210197371695123</v>
+        <v>0.08940379044054639</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.03531574651317242</v>
+        <v>-0.2221661969964162</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.03391435740103591</v>
+        <v>0.1418176003039721</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.003532563844474296</v>
+        <v>-0.03954314121581561</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.00800320829410152</v>
+        <v>0.3488679216806419</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.006610866519397472</v>
+        <v>-0.1847785072457316</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.01631024947911528</v>
+        <v>0.2851599745447508</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.006098666960557544</v>
+        <v>0.006130310389735823</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0003246674849548178</v>
+        <v>0.08912753497891127</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.03548492396418154</v>
+        <v>-0.09927253597834998</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.02308780334112119</v>
+        <v>-0.194549181245576</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.001559574311184672</v>
+        <v>-0.08116691836157176</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,10 +5551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.6333321328806398</v>
+        <v>-0.2084792159555122</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -5563,13 +5563,13 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1440645318562985</v>
+        <v>-0.006384425030151558</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9478170162920985</v>
+        <v>0.189834941200862</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5578,10 +5578,10 @@
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2768047235892421</v>
+        <v>-0.1096166751430972</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
@@ -5590,10 +5590,10 @@
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.04714759552105241</v>
+        <v>0.04994366285250167</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6130080528745286</v>
+        <v>0.1275513823510485</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5608,22 +5608,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.08987364958049784</v>
+        <v>-0.07447894772877092</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.09929075318987055</v>
+        <v>-0.01028612858590421</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01322540642381054</v>
+        <v>-0.03034365880860297</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -5632,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.2292662844646398</v>
+        <v>0.04934224178435086</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
@@ -5644,10 +5644,10 @@
         <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.009041921356546138</v>
+        <v>0.1325664531607018</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1794684588853131</v>
+        <v>0.02895627485620352</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.1023697505229313</v>
+        <v>-0.1064408785403294</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.133995609998641</v>
+        <v>-0.06988470441452106</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2848560101649846</v>
+        <v>0.1473352732760574</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.3965576578619361</v>
+        <v>-0.2712167576070214</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,25 +5698,25 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3715169595648701</v>
+        <v>0.08545254241921577</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.898446928044848</v>
+        <v>0.1229258411756775</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.407520166372013</v>
+        <v>0.08502860584449448</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
@@ -5725,25 +5725,25 @@
         <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.1853226290135963</v>
+        <v>0.1992327461192683</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.1937053163495445</v>
+        <v>0.1106634423137898</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.1100656542514048</v>
+        <v>0.01639344190314307</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,10 +5752,10 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.1007975938249138</v>
+        <v>-0.05520747974159876</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.003827582056926658</v>
+        <v>-0.04510861521099055</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -5770,25 +5770,25 @@
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.2135037216207077</v>
+        <v>-0.2043496119656293</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1011905607977777</v>
+        <v>0.004108661655667133</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.3343115544923815</v>
+        <v>0.08431087855857648</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1917405269793536</v>
+        <v>0.1225254342914704</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,10 +5806,10 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01392885338782887</v>
+        <v>-0.01319583423710121</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.1923463616915325</v>
+        <v>-0.07743273012909681</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
@@ -5818,28 +5818,28 @@
         <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01870983651228235</v>
+        <v>0.0735202445044103</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.2128664555115923</v>
+        <v>-0.1443724349365737</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1178104982967436</v>
+        <v>-0.04107696025664406</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
@@ -5848,10 +5848,10 @@
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1588111466996637</v>
+        <v>0.1107408049406598</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.06267377383661794</v>
+        <v>-0.01041636696222213</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.2316167622665714</v>
+        <v>-0.06522510937247344</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
@@ -5878,52 +5878,52 @@
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01400185717823196</v>
+        <v>-0.003995657365040254</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.2584495789923995</v>
+        <v>0.0498187860226145</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.03326402031973864</v>
+        <v>-0.01065246494434375</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.1236803356152932</v>
+        <v>0.02124188153493036</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1041139570545863</v>
+        <v>0.007669797168659903</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.06952409350688951</v>
+        <v>-0.02506587373349488</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1309708494361494</v>
+        <v>-0.03391614190114071</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.2929865533099328</v>
+        <v>0.0497579787310474</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.1000511045917228</v>
+        <v>0.02212487484629061</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -5953,25 +5953,25 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0793975541923761</v>
+        <v>0.05819865071308115</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.1459935794740662</v>
+        <v>0.01846939864496878</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.1644080759119566</v>
+        <v>-0.01011193822996479</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
@@ -5980,13 +5980,13 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1711079067931622</v>
+        <v>0.09367782183312537</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,25 +5995,25 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.08809072694169402</v>
+        <v>0.07162776965567434</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.006277793455702759</v>
+        <v>0.09626699634157608</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.178110070323006</v>
+        <v>0.1272744353608633</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,13 +6022,13 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.05886863043145255</v>
+        <v>-0.003162623344727291</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.2320116557213362</v>
+        <v>-0.06032154245826478</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01800079849460328</v>
+        <v>0.1259115030178628</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,37 +6049,37 @@
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01501975987369351</v>
+        <v>-0.04267275441389723</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.2392463723158225</v>
+        <v>-0.0993115145385092</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.008423739451268418</v>
+        <v>0.1100794135240663</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1484080108072988</v>
+        <v>-0.01005489410683047</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.3303382599966145</v>
+        <v>-0.07058023032862215</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
@@ -6094,10 +6094,10 @@
         <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.1283005601406513</v>
+        <v>0.113629337868941</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0872130603933849</v>
+        <v>0.03830205089082456</v>
       </c>
       <c r="GE10" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1333747704097537</v>
+        <v>0.5148325973131788</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.006346353310403234</v>
+        <v>0.0002700440850149603</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09238705329937291</v>
+        <v>-0.280564342159551</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6147,10 +6147,10 @@
         <v>-0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1074339899046069</v>
+        <v>0.6075606347199339</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.004922750975620268</v>
+        <v>-0.1269468041886106</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06333348995726427</v>
+        <v>-0.1982353532227623</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.007850565653307266</v>
+        <v>0.1139995950450614</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01521090670274852</v>
+        <v>-0.004443227824983744</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01571716032506547</v>
+        <v>-0.1177768790472474</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.008316099349665495</v>
+        <v>0.03215875159809943</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01235721675422421</v>
+        <v>-0.06130712917934466</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01731685655992342</v>
+        <v>0.07795744972795222</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.006742006836319209</v>
+        <v>0.1657124953135528</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.008719181063579343</v>
+        <v>0.06451357517745945</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04350250535089837</v>
+        <v>-0.09482639186049169</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1091571088354197</v>
+        <v>0.7338388647635505</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.00885172471062848</v>
+        <v>-0.2759153201846885</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.06423155134413359</v>
+        <v>-0.3212020212138874</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05188276019307981</v>
+        <v>-0.1839698045602423</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.02485971350127424</v>
+        <v>0.01335580953829206</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.05555194651347658</v>
+        <v>-0.0419011910793562</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6306,52 +6306,52 @@
         <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03996804065148661</v>
+        <v>0.009174731277238977</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01419698175298306</v>
+        <v>0.089843474575002</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01794783304865634</v>
+        <v>0.04391066948069087</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.05605944782850338</v>
+        <v>0.4384048668309342</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.002626131867736737</v>
+        <v>-0.03677873754959628</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.02406693501916508</v>
+        <v>-0.1703999915772176</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,25 +6366,25 @@
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02983591228312463</v>
+        <v>-0.2394700460300695</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.00271046045514352</v>
+        <v>0.017515858575498</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02423289219041722</v>
+        <v>0.1075699391986752</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.008574699962323611</v>
+        <v>-0.09829052415643967</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.00351575685253533</v>
+        <v>0.07772980135248647</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.008853434160957165</v>
+        <v>0.04492254828031166</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.0223002523975217</v>
+        <v>-0.2237061299253223</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.0022845470218262</v>
+        <v>0.01441453771117305</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02978972586931386</v>
+        <v>0.1233328294515248</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.004042153493190569</v>
+        <v>0.01108555135666103</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.008102356115746018</v>
+        <v>0.02229123519137749</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0126818434258586</v>
+        <v>0.09452965097261611</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6471,28 +6471,28 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0117108452349807</v>
+        <v>-0.08465824679981289</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.007697112199631012</v>
+        <v>-0.0183323931389147</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.004775339957483572</v>
+        <v>0.08594244480854549</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.03625581567067365</v>
+        <v>-0.1572603468630954</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.009218750434680942</v>
+        <v>0.06259317427101001</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01784494534518465</v>
+        <v>-0.1024368562931136</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02071768898491964</v>
+        <v>-0.1283539480535044</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.003104876901817064</v>
+        <v>-0.05031721999726278</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0156409895730309</v>
+        <v>0.0412747467355729</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.007571463270012959</v>
+        <v>0.0938704795640192</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.003932367996226053</v>
+        <v>0.0142643575323563</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001880821807891714</v>
+        <v>-0.04128950148844369</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,52 +6576,52 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02198731072545749</v>
+        <v>-0.2578804784633106</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001206428374172076</v>
+        <v>-0.007625591026963668</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03021805443850384</v>
+        <v>0.1250087453308819</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.003380217103684103</v>
+        <v>-0.1260089855804763</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01607362177234817</v>
+        <v>-0.01451814246354441</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02992896954521935</v>
+        <v>0.1362518640586858</v>
       </c>
       <c r="FM11" t="n">
         <v>-0</v>
@@ -6636,7 +6636,7 @@
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.0196555951489811</v>
+        <v>-0.2368096317537156</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02443977178562185</v>
+        <v>-0.06122378289717301</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.0008763209283351258</v>
+        <v>-0.0101744704646738</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01311891922634132</v>
+        <v>-0.1134967812113027</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02613882249697758</v>
+        <v>0.07198302679113594</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3595239659945326</v>
+        <v>-0.3737637328004914</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1918948061953517</v>
+        <v>0.1326478602353585</v>
       </c>
       <c r="E12" t="n">
-        <v>0.217961686878524</v>
+        <v>0.07984689236739811</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
@@ -6713,25 +6713,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.290603672443886</v>
+        <v>-0.4559974253514154</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2105292914795927</v>
+        <v>0.223032096262105</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2389788726610567</v>
+        <v>0.1539367503506809</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -6746,25 +6746,25 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1015994294792082</v>
+        <v>-0.0402388324492669</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01694052201451101</v>
+        <v>0.01267256161566748</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.04183647001244236</v>
+        <v>-0.005544661424828436</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>-0</v>
@@ -6773,22 +6773,22 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1524543817303817</v>
+        <v>-0.01986218768638529</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.05730643156480612</v>
+        <v>0.1338706937573633</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.03112473842292171</v>
+        <v>-0.2222037577602377</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -6797,76 +6797,76 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.03530618224662264</v>
+        <v>-0.1467362683141169</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.04496369266459647</v>
+        <v>0.03771858075953894</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.07773047799036843</v>
+        <v>-0.2313778420852493</v>
       </c>
       <c r="AP12" t="n">
         <v>-0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.2823760744888923</v>
+        <v>-0.2428530737293749</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.009386233642463646</v>
+        <v>0.140834232216819</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.01912585227520819</v>
+        <v>0.02256290232743481</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01270378074326078</v>
+        <v>0.05066757266978159</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.1947370835745189</v>
+        <v>0.01267303549555298</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.2801864307627785</v>
+        <v>0.131204742198662</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
@@ -6881,16 +6881,16 @@
         <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.09746939744970234</v>
+        <v>0.1121550478169164</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.03966367599017617</v>
+        <v>0.08290456634644046</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.1006469971429728</v>
+        <v>0.001854649371135884</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -6908,25 +6908,25 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.2214552231237848</v>
+        <v>-0.1967383025962886</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.001954980983664282</v>
+        <v>0.06910249671461589</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.04295490695730891</v>
+        <v>-0.0085159241749709</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,25 +6935,25 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.09111559250187642</v>
+        <v>0.1941410410625169</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.04630099311145542</v>
+        <v>-0.05770707510185234</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.002501104486842532</v>
+        <v>-0.004755495526076575</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03036194770759994</v>
+        <v>0.089814116304601</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.06177633397348618</v>
+        <v>-0.08566313376769037</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.08264093758651204</v>
+        <v>-0.03688885645439984</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS12" t="n">
         <v>0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.08768772856841285</v>
+        <v>0.203680935099142</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>-0.06427216599515229</v>
+        <v>-0.05883352196937213</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.003251567564702623</v>
+        <v>-0.03258943965871855</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,52 +7016,52 @@
         <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.1674791704590838</v>
+        <v>0.1516227042501961</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0.05120534549396998</v>
+        <v>-0.02342471104732869</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.008569236863323306</v>
+        <v>-0.000970404644517681</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
         <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0444027720261606</v>
+        <v>0.09032915425264003</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03951346969164644</v>
+        <v>-0.04203099856430466</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.06924336164510286</v>
+        <v>0.02707078849941816</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
         <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>-0</v>
@@ -7070,22 +7070,22 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1020258637098203</v>
+        <v>0.04218837314236253</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.09150862549650279</v>
+        <v>0.04949671606083903</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.05065278254419057</v>
+        <v>0.006867971764129158</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED12" t="n">
         <v>-0</v>
@@ -7097,22 +7097,22 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.05382829121024003</v>
+        <v>0.2267285513372236</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.04169300521635982</v>
+        <v>-0.0568662035802833</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.1036737619249987</v>
+        <v>-0.03789969876844101</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM12" t="n">
         <v>0</v>
@@ -7121,28 +7121,28 @@
         <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0004639062558998706</v>
+        <v>-0.1168263580159574</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03281302057021471</v>
+        <v>-0.01012929929656321</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02831961310528018</v>
+        <v>0.004782772460820705</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
@@ -7151,16 +7151,16 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.09068410370469708</v>
+        <v>0.2302553806432373</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.05954802278726774</v>
+        <v>-0.0707934113191805</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.005773934316406578</v>
+        <v>-0.0006280483128592738</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
@@ -7169,52 +7169,52 @@
         <v>-0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.05169731641457217</v>
+        <v>0.08428186888562736</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.08810583646586569</v>
+        <v>0.1085450814762721</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04179208425015184</v>
+        <v>0.03676015370198812</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.02522769737549652</v>
+        <v>0.1785516605937419</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03322027598198776</v>
+        <v>0.01260390136827294</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.009205554983633504</v>
+        <v>-0.05637390529607172</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7223,37 +7223,37 @@
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.05225639164725931</v>
+        <v>0.2022148667834</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.06616922842704878</v>
+        <v>-0.001531745628289719</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
         <v>0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,16 +7270,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,16 +7324,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,52 +7432,52 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,22 +7504,22 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,100 +7531,100 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,106 +7648,106 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,46 +7774,46 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,25 +9004,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,40 +9031,40 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X16" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,22 +9076,22 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,28 +9100,28 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,52 +9139,52 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,31 +9205,31 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -9238,52 +9238,52 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
@@ -9292,22 +9292,22 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>-0</v>
@@ -9316,28 +9316,28 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>-0</v>
@@ -9346,49 +9346,49 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9397,82 +9397,82 @@
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,63 +9481,63 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,10 +9546,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9558,10 +9558,10 @@
         <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K17" t="n">
         <v>-0</v>
@@ -9570,43 +9570,43 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>-0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -9624,43 +9624,43 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -9669,25 +9669,25 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
@@ -9696,22 +9696,22 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI17" t="n">
         <v>0</v>
@@ -9723,10 +9723,10 @@
         <v>-0</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN17" t="n">
         <v>-0</v>
@@ -9735,37 +9735,37 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
       </c>
       <c r="BW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE17" t="n">
         <v>0</v>
@@ -9789,13 +9789,13 @@
         <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9804,25 +9804,25 @@
         <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
         <v>-0</v>
@@ -9831,7 +9831,7 @@
         <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW17" t="n">
         <v>-0</v>
@@ -9843,40 +9843,40 @@
         <v>-0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
@@ -9885,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO17" t="n">
         <v>0</v>
@@ -9894,13 +9894,13 @@
         <v>0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
@@ -9909,37 +9909,37 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY17" t="n">
         <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE17" t="n">
         <v>0</v>
       </c>
       <c r="EF17" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG17" t="n">
         <v>0</v>
@@ -9951,22 +9951,22 @@
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP17" t="n">
         <v>0</v>
@@ -9975,13 +9975,13 @@
         <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9993,7 +9993,7 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY17" t="n">
         <v>0</v>
@@ -10005,22 +10005,22 @@
         <v>0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH17" t="n">
         <v>-0</v>
@@ -10029,13 +10029,13 @@
         <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10047,10 +10047,10 @@
         <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,13 +10059,13 @@
         <v>0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
         <v>-0</v>
@@ -10074,28 +10074,28 @@
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
